--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -6760,23 +6760,51 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B5" s="123" t="n"/>
+      <c r="B5" s="123" t="n">
+        <v>1540792</v>
+      </c>
       <c r="C5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="123" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="123" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="123" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="123" t="n"/>
-      <c r="K5" s="59" t="n"/>
-      <c r="L5" s="123" t="n"/>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="123" t="n"/>
-      <c r="O5" s="20" t="n"/>
-      <c r="P5" s="124" t="n"/>
+      <c r="D5" s="123" t="n">
+        <v>168201</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="F5" s="123" t="n">
+        <v>1099814</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>0.7138</v>
+      </c>
+      <c r="H5" s="123" t="n">
+        <v>78537</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="J5" s="123" t="n">
+        <v>30187</v>
+      </c>
+      <c r="K5" s="59" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="L5" s="123" t="n">
+        <v>196195</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="N5" s="123" t="n">
+        <v>42470</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="P5" s="124" t="n">
+        <v>1235086</v>
+      </c>
     </row>
     <row r="6" ht="23.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -7205,22 +7233,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B6" s="140" t="n"/>
-      <c r="C6" s="135" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="137" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="66" t="n"/>
-      <c r="I6" s="51" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="66" t="n"/>
-      <c r="L6" s="52" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="66" t="n"/>
-      <c r="O6" s="50" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="66" t="n"/>
+      <c r="B6" s="140" t="n">
+        <v>1540792</v>
+      </c>
+      <c r="C6" s="135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>242697</v>
+      </c>
+      <c r="E6" s="64" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="F6" s="137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>221845</v>
+      </c>
+      <c r="H6" s="66" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="I6" s="51" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>191414</v>
+      </c>
+      <c r="K6" s="66" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="L6" s="52" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>182787</v>
+      </c>
+      <c r="N6" s="66" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="O6" s="50" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n">
+        <v>171831</v>
+      </c>
+      <c r="Q6" s="66" t="n">
+        <v>0.1115</v>
+      </c>
       <c r="S6" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -7750,22 +7820,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B5" s="157" t="n"/>
-      <c r="C5" s="43" t="n"/>
-      <c r="D5" s="141" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="42" t="n"/>
-      <c r="G5" s="141" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="44" t="n"/>
-      <c r="J5" s="141" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="141" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="158" t="n"/>
-      <c r="P5" s="142" t="n"/>
-      <c r="Q5" s="32" t="n"/>
+      <c r="B5" s="157" t="n">
+        <v>168201</v>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="141" t="n">
+        <v>40792</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G5" s="141" t="n">
+        <v>20225</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="I5" s="44" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J5" s="141" t="n">
+        <v>18618</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M5" s="141" t="n">
+        <v>18588</v>
+      </c>
+      <c r="N5" s="32" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="O5" s="158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" s="142" t="n">
+        <v>14290</v>
+      </c>
+      <c r="Q5" s="32" t="n">
+        <v>0.08500000000000001</v>
+      </c>
       <c r="S5" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -8302,22 +8414,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B5" s="157" t="n"/>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="141" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="163" t="n"/>
-      <c r="G5" s="141" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="162" t="n"/>
-      <c r="J5" s="141" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="38" t="n"/>
-      <c r="M5" s="141" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="161" t="n"/>
-      <c r="P5" s="141" t="n"/>
-      <c r="Q5" s="32" t="n"/>
+      <c r="B5" s="157" t="n">
+        <v>196195</v>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D5" s="141" t="n">
+        <v>48448</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>0.2469</v>
+      </c>
+      <c r="F5" s="163" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G5" s="141" t="n">
+        <v>43459</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="I5" s="162" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J5" s="141" t="n">
+        <v>29026</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="L5" s="38" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M5" s="141" t="n">
+        <v>25670</v>
+      </c>
+      <c r="N5" s="19" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="O5" s="161" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="P5" s="141" t="n">
+        <v>2917</v>
+      </c>
+      <c r="Q5" s="32" t="n">
+        <v>0.0149</v>
+      </c>
       <c r="S5" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -8854,22 +9008,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="162" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="161" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="163" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>1099814</v>
+      </c>
+      <c r="C6" s="162" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>207778</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>138361</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="I6" s="161" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>132253</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="L6" s="163" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>124510</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="O6" s="46" t="inlineStr">
+        <is>
+          <t>TRANSFER. / DEPTOS.</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n">
+        <v>94503</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>0.0859</v>
+      </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -9406,22 +9602,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="162" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="163" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="139" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>78537</v>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>15070</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="F6" s="162" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>13953</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>12635</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="L6" s="163" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>11636</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="O6" s="139" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n">
+        <v>11411</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>0.1453</v>
+      </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -9958,22 +10196,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="162" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="161" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="163" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>1235086</v>
+      </c>
+      <c r="C6" s="162" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>226499</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>153573</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="I6" s="161" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>147563</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="L6" s="163" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>138495</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="O6" s="46" t="inlineStr">
+        <is>
+          <t>TRANSFER. / DEPTOS.</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n">
+        <v>105867</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>0.0857</v>
+      </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -10494,22 +10774,64 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B5" s="157" t="n"/>
-      <c r="C5" s="144" t="n"/>
-      <c r="D5" s="141" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="152" t="n"/>
-      <c r="G5" s="141" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="145" t="n"/>
-      <c r="J5" s="141" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="141" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="56" t="n"/>
-      <c r="P5" s="142" t="n"/>
-      <c r="Q5" s="32" t="n"/>
+      <c r="B5" s="157" t="n">
+        <v>30187</v>
+      </c>
+      <c r="C5" s="144" t="inlineStr">
+        <is>
+          <t>TRANSFER. / DEPTOS.</t>
+        </is>
+      </c>
+      <c r="D5" s="141" t="n">
+        <v>8755</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F5" s="152" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="G5" s="141" t="n">
+        <v>5235</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="I5" s="145" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J5" s="141" t="n">
+        <v>4336</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="M5" s="141" t="n">
+        <v>3258</v>
+      </c>
+      <c r="N5" s="32" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="O5" s="56" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="P5" s="142" t="n">
+        <v>3050</v>
+      </c>
+      <c r="Q5" s="32" t="n">
+        <v>0.101</v>
+      </c>
       <c r="S5" s="139" t="inlineStr">
         <is>
           <t>EDGAR</t>
@@ -10973,14 +11295,30 @@
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="B6" s="141" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="141" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="141" t="n"/>
-      <c r="I6" s="19" t="n"/>
+      <c r="B6" s="141" t="n">
+        <v>1217167</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>121717</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="141" t="n">
+        <v>912875</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="141" t="n">
+        <v>182575</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1">
       <c r="A7" s="10" t="inlineStr">

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -6812,21 +6812,47 @@
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B6" s="125" t="n"/>
-      <c r="C6" s="61" t="n"/>
-      <c r="D6" s="125" t="n"/>
-      <c r="E6" s="61" t="n"/>
-      <c r="F6" s="125" t="n"/>
-      <c r="G6" s="61" t="n"/>
-      <c r="H6" s="125" t="n"/>
-      <c r="I6" s="61" t="n"/>
-      <c r="J6" s="125" t="n"/>
-      <c r="K6" s="21" t="n"/>
-      <c r="L6" s="125" t="n"/>
-      <c r="M6" s="61" t="n"/>
+      <c r="B6" s="125" t="n">
+        <v>1526774</v>
+      </c>
+      <c r="C6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="125" t="n">
+        <v>173525</v>
+      </c>
+      <c r="E6" s="61" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="F6" s="125" t="n">
+        <v>1072227</v>
+      </c>
+      <c r="G6" s="61" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="H6" s="125" t="n">
+        <v>115936</v>
+      </c>
+      <c r="I6" s="61" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J6" s="125" t="n">
+        <v>1958</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="L6" s="125" t="n">
+        <v>224216</v>
+      </c>
+      <c r="M6" s="61" t="n">
+        <v>0.1817</v>
+      </c>
       <c r="N6" s="125" t="n"/>
       <c r="O6" s="61" t="n"/>
-      <c r="P6" s="126" t="n"/>
+      <c r="P6" s="126" t="n">
+        <v>1233658</v>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -6834,21 +6860,47 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B7" s="125" t="n"/>
-      <c r="C7" s="61" t="n"/>
-      <c r="D7" s="125" t="n"/>
-      <c r="E7" s="61" t="n"/>
-      <c r="F7" s="125" t="n"/>
-      <c r="G7" s="61" t="n"/>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="61" t="n"/>
-      <c r="J7" s="125" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="125" t="n"/>
-      <c r="M7" s="61" t="n"/>
+      <c r="B7" s="125" t="n">
+        <v>1390390</v>
+      </c>
+      <c r="C7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="125" t="n">
+        <v>139123</v>
+      </c>
+      <c r="E7" s="61" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F7" s="125" t="n">
+        <v>974194</v>
+      </c>
+      <c r="G7" s="61" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="H7" s="125" t="n">
+        <v>83974</v>
+      </c>
+      <c r="I7" s="61" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J7" s="125" t="n">
+        <v>4409</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L7" s="125" t="n">
+        <v>230082</v>
+      </c>
+      <c r="M7" s="61" t="n">
+        <v>0.2083</v>
+      </c>
       <c r="N7" s="125" t="n"/>
       <c r="O7" s="61" t="n"/>
-      <c r="P7" s="126" t="n"/>
+      <c r="P7" s="126" t="n">
+        <v>1104502</v>
+      </c>
     </row>
     <row r="8" ht="23.25" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -6856,21 +6908,47 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B8" s="125" t="n"/>
-      <c r="C8" s="61" t="n"/>
-      <c r="D8" s="125" t="n"/>
-      <c r="E8" s="61" t="n"/>
-      <c r="F8" s="125" t="n"/>
-      <c r="G8" s="61" t="n"/>
-      <c r="H8" s="125" t="n"/>
-      <c r="I8" s="61" t="n"/>
-      <c r="J8" s="125" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="125" t="n"/>
-      <c r="M8" s="61" t="n"/>
+      <c r="B8" s="125" t="n">
+        <v>1478249</v>
+      </c>
+      <c r="C8" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="125" t="n">
+        <v>156032</v>
+      </c>
+      <c r="E8" s="61" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="F8" s="125" t="n">
+        <v>1094875</v>
+      </c>
+      <c r="G8" s="61" t="n">
+        <v>0.7929</v>
+      </c>
+      <c r="H8" s="125" t="n">
+        <v>160622</v>
+      </c>
+      <c r="I8" s="61" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="J8" s="125" t="n">
+        <v>8829</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="L8" s="125" t="n">
+        <v>175501</v>
+      </c>
+      <c r="M8" s="61" t="n">
+        <v>0.1271</v>
+      </c>
       <c r="N8" s="125" t="n"/>
       <c r="O8" s="61" t="n"/>
-      <c r="P8" s="126" t="n"/>
+      <c r="P8" s="126" t="n">
+        <v>1380870</v>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -7230,11 +7308,11 @@
     <row r="6" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B6" s="140" t="n">
-        <v>1540792</v>
+        <v>1526774</v>
       </c>
       <c r="C6" s="135" t="inlineStr">
         <is>
@@ -7242,10 +7320,10 @@
         </is>
       </c>
       <c r="D6" s="141" t="n">
-        <v>242697</v>
+        <v>269023</v>
       </c>
       <c r="E6" s="64" t="n">
-        <v>0.1575</v>
+        <v>0.1762</v>
       </c>
       <c r="F6" s="137" t="inlineStr">
         <is>
@@ -7253,32 +7331,32 @@
         </is>
       </c>
       <c r="G6" s="141" t="n">
-        <v>221845</v>
+        <v>253220</v>
       </c>
       <c r="H6" s="66" t="n">
-        <v>0.144</v>
+        <v>0.1659</v>
       </c>
       <c r="I6" s="51" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>193059</v>
+      </c>
+      <c r="K6" s="66" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="L6" s="52" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="J6" s="141" t="n">
-        <v>191414</v>
-      </c>
-      <c r="K6" s="66" t="n">
-        <v>0.1242</v>
-      </c>
-      <c r="L6" s="52" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="M6" s="141" t="n">
-        <v>182787</v>
+        <v>175269</v>
       </c>
       <c r="N6" s="66" t="n">
-        <v>0.1186</v>
+        <v>0.1148</v>
       </c>
       <c r="O6" s="50" t="inlineStr">
         <is>
@@ -7286,10 +7364,10 @@
         </is>
       </c>
       <c r="P6" s="142" t="n">
-        <v>171831</v>
+        <v>160304</v>
       </c>
       <c r="Q6" s="66" t="n">
-        <v>0.1115</v>
+        <v>0.105</v>
       </c>
       <c r="S6" s="143" t="inlineStr">
         <is>
@@ -7300,25 +7378,67 @@
     <row r="7" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B7" s="140" t="n"/>
-      <c r="C7" s="135" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="137" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="66" t="n"/>
-      <c r="I7" s="51" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="66" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="66" t="n"/>
-      <c r="O7" s="26" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="66" t="n"/>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B7" s="140" t="n">
+        <v>1390390</v>
+      </c>
+      <c r="C7" s="135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>250821</v>
+      </c>
+      <c r="E7" s="64" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="F7" s="137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>241709</v>
+      </c>
+      <c r="H7" s="66" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="I7" s="51" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>188520</v>
+      </c>
+      <c r="K7" s="66" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>171847</v>
+      </c>
+      <c r="N7" s="66" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="O7" s="26" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="n">
+        <v>125413</v>
+      </c>
+      <c r="Q7" s="66" t="n">
+        <v>0.0902</v>
+      </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -7328,25 +7448,67 @@
     <row r="8" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B8" s="140" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="66" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="66" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="66" t="n"/>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B8" s="140" t="n">
+        <v>1478249</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>265237</v>
+      </c>
+      <c r="E8" s="64" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>255144</v>
+      </c>
+      <c r="H8" s="66" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>209441</v>
+      </c>
+      <c r="K8" s="66" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>153986</v>
+      </c>
+      <c r="N8" s="66" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>118762</v>
+      </c>
+      <c r="Q8" s="66" t="n">
+        <v>0.0803</v>
+      </c>
       <c r="S8" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -7890,22 +8052,64 @@
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="43" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="145" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>173525</v>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>39717</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="F6" s="145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>19278</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>19129</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>18265</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n">
+        <v>17176</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>0.099</v>
+      </c>
       <c r="S6" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -7918,22 +8122,64 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="33" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="33" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="32" t="n"/>
-      <c r="O7" s="33" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="32" t="n"/>
+      <c r="B7" s="157" t="n">
+        <v>139123</v>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>28361</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>21423</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>14130</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="L7" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>13977</v>
+      </c>
+      <c r="N7" s="32" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="O7" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="n">
+        <v>12920</v>
+      </c>
+      <c r="Q7" s="32" t="n">
+        <v>0.0929</v>
+      </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -7946,22 +8192,64 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+      <c r="B8" s="157" t="n">
+        <v>156032</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>36123</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>18699</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>16975</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>13496</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>13030</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.0835</v>
+      </c>
       <c r="S8" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -8484,22 +8772,64 @@
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="144" t="n"/>
-      <c r="J6" s="141" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="143" t="n"/>
-      <c r="M6" s="141" t="n"/>
-      <c r="N6" s="19" t="n"/>
-      <c r="O6" s="139" t="n"/>
-      <c r="P6" s="141" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>224216</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>53733</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>41602</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="I6" s="144" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>35556</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="L6" s="143" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>29163</v>
+      </c>
+      <c r="N6" s="19" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="O6" s="139" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="P6" s="141" t="n">
+        <v>22671</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>0.1011</v>
+      </c>
       <c r="S6" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -8512,22 +8842,64 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="33" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="33" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="33" t="n"/>
-      <c r="P7" s="141" t="n"/>
-      <c r="Q7" s="32" t="n"/>
+      <c r="B7" s="157" t="n">
+        <v>230082</v>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>54948</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>42708</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>42545</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="L7" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>27064</v>
+      </c>
+      <c r="N7" s="19" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="O7" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P7" s="141" t="n">
+        <v>25386</v>
+      </c>
+      <c r="Q7" s="32" t="n">
+        <v>0.1103</v>
+      </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -8540,22 +8912,64 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="19" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="141" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+      <c r="B8" s="157" t="n">
+        <v>175501</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>32199</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>28081</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>26424</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>19859</v>
+      </c>
+      <c r="N8" s="19" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="P8" s="141" t="n">
+        <v>17014</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.0969</v>
+      </c>
       <c r="S8" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -9005,11 +9419,11 @@
     <row r="6" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B6" s="157" t="n">
-        <v>1099814</v>
+        <v>1072227</v>
       </c>
       <c r="C6" s="162" t="inlineStr">
         <is>
@@ -9017,10 +9431,10 @@
         </is>
       </c>
       <c r="D6" s="141" t="n">
-        <v>207778</v>
+        <v>227288</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>0.1889</v>
+        <v>0.212</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
@@ -9028,10 +9442,10 @@
         </is>
       </c>
       <c r="G6" s="141" t="n">
-        <v>138361</v>
+        <v>145846</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.1258</v>
+        <v>0.136</v>
       </c>
       <c r="I6" s="161" t="inlineStr">
         <is>
@@ -9039,32 +9453,32 @@
         </is>
       </c>
       <c r="J6" s="141" t="n">
-        <v>132253</v>
+        <v>132480</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>0.1203</v>
+        <v>0.1236</v>
       </c>
       <c r="L6" s="163" t="inlineStr">
         <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>112573</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O6" s="46" t="inlineStr">
+        <is>
           <t>OFICINA</t>
         </is>
       </c>
-      <c r="M6" s="141" t="n">
-        <v>124510</v>
-      </c>
-      <c r="N6" s="32" t="n">
-        <v>0.1132</v>
-      </c>
-      <c r="O6" s="46" t="inlineStr">
-        <is>
-          <t>TRANSFER. / DEPTOS.</t>
-        </is>
-      </c>
       <c r="P6" s="142" t="n">
-        <v>94503</v>
+        <v>95439</v>
       </c>
       <c r="Q6" s="32" t="n">
-        <v>0.0859</v>
+        <v>0.089</v>
       </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
@@ -9075,25 +9489,67 @@
     <row r="7" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="162" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="161" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="46" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="32" t="n"/>
-      <c r="O7" s="163" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="32" t="n"/>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B7" s="157" t="n">
+        <v>974194</v>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>171224</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="F7" s="162" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>134042</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="I7" s="161" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>133769</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="L7" s="46" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>115260</v>
+      </c>
+      <c r="N7" s="32" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="O7" s="163" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="n">
+        <v>86460</v>
+      </c>
+      <c r="Q7" s="32" t="n">
+        <v>0.0888</v>
+      </c>
       <c r="S7" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -9103,25 +9559,67 @@
     <row r="8" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B8" s="157" t="n">
+        <v>1094875</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>162181</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>129205</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>110249</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>107329</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>99723</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.0911</v>
+      </c>
       <c r="S8" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -9599,66 +10097,66 @@
     <row r="6" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B6" s="157" t="n">
-        <v>78537</v>
+        <v>115936</v>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>32985</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="F6" s="162" t="inlineStr">
+        <is>
           <t>EDGAR</t>
         </is>
       </c>
-      <c r="D6" s="141" t="n">
-        <v>15070</v>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>0.1919</v>
-      </c>
-      <c r="F6" s="162" t="inlineStr">
+      <c r="G6" s="141" t="n">
+        <v>30163</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J6" s="141" t="n">
+        <v>21237</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="L6" s="163" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>9939</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="O6" s="139" t="inlineStr">
         <is>
           <t>V39</t>
         </is>
       </c>
-      <c r="G6" s="141" t="n">
-        <v>13953</v>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>0.1777</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>FRANCISCO</t>
-        </is>
-      </c>
-      <c r="J6" s="141" t="n">
-        <v>12635</v>
-      </c>
-      <c r="K6" s="32" t="n">
-        <v>0.1609</v>
-      </c>
-      <c r="L6" s="163" t="inlineStr">
-        <is>
-          <t>EDUARDO</t>
-        </is>
-      </c>
-      <c r="M6" s="141" t="n">
-        <v>11636</v>
-      </c>
-      <c r="N6" s="32" t="n">
-        <v>0.1482</v>
-      </c>
-      <c r="O6" s="139" t="inlineStr">
-        <is>
-          <t>JORGE</t>
-        </is>
-      </c>
       <c r="P6" s="142" t="n">
-        <v>11411</v>
+        <v>5055</v>
       </c>
       <c r="Q6" s="32" t="n">
-        <v>0.1453</v>
+        <v>0.0436</v>
       </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
@@ -9669,25 +10167,67 @@
     <row r="7" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="163" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="139" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="32" t="n"/>
-      <c r="O7" s="18" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="32" t="n"/>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B7" s="157" t="n">
+        <v>83974</v>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>24192</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="F7" s="163" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>12023</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="I7" s="139" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>12012</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>9901</v>
+      </c>
+      <c r="N7" s="32" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="n">
+        <v>8938</v>
+      </c>
+      <c r="Q7" s="32" t="n">
+        <v>0.1064</v>
+      </c>
       <c r="S7" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -9697,25 +10237,67 @@
     <row r="8" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B8" s="157" t="n">
+        <v>160622</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>58029</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>34324</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.2137</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>19500</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>15838</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>13004</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.081</v>
+      </c>
       <c r="S8" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -10193,11 +10775,11 @@
     <row r="6" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B6" s="157" t="n">
-        <v>1235086</v>
+        <v>1233658</v>
       </c>
       <c r="C6" s="162" t="inlineStr">
         <is>
@@ -10205,10 +10787,10 @@
         </is>
       </c>
       <c r="D6" s="141" t="n">
-        <v>226499</v>
+        <v>264733</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>0.1834</v>
+        <v>0.2146</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
@@ -10216,10 +10798,10 @@
         </is>
       </c>
       <c r="G6" s="141" t="n">
-        <v>153573</v>
+        <v>169345</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.1243</v>
+        <v>0.1373</v>
       </c>
       <c r="I6" s="161" t="inlineStr">
         <is>
@@ -10227,32 +10809,32 @@
         </is>
       </c>
       <c r="J6" s="141" t="n">
-        <v>147563</v>
+        <v>167542</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>0.1195</v>
+        <v>0.1358</v>
       </c>
       <c r="L6" s="163" t="inlineStr">
         <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M6" s="141" t="n">
+        <v>123218</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="O6" s="46" t="inlineStr">
+        <is>
           <t>OFICINA</t>
         </is>
       </c>
-      <c r="M6" s="141" t="n">
-        <v>138495</v>
-      </c>
-      <c r="N6" s="32" t="n">
-        <v>0.1121</v>
-      </c>
-      <c r="O6" s="46" t="inlineStr">
-        <is>
-          <t>TRANSFER. / DEPTOS.</t>
-        </is>
-      </c>
       <c r="P6" s="142" t="n">
-        <v>105867</v>
+        <v>106327</v>
       </c>
       <c r="Q6" s="32" t="n">
-        <v>0.0857</v>
+        <v>0.0862</v>
       </c>
       <c r="S6" s="139" t="inlineStr">
         <is>
@@ -10263,25 +10845,67 @@
     <row r="7" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="162" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="161" t="n"/>
-      <c r="J7" s="141" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="46" t="n"/>
-      <c r="M7" s="141" t="n"/>
-      <c r="N7" s="32" t="n"/>
-      <c r="O7" s="163" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="32" t="n"/>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="B7" s="157" t="n">
+        <v>1104502</v>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>189373</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="F7" s="162" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>164326</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="I7" s="161" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J7" s="141" t="n">
+        <v>145344</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="L7" s="46" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M7" s="141" t="n">
+        <v>131931</v>
+      </c>
+      <c r="N7" s="32" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="O7" s="163" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="n">
+        <v>95852</v>
+      </c>
+      <c r="Q7" s="32" t="n">
+        <v>0.0868</v>
+      </c>
       <c r="S7" s="143" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -10291,25 +10915,67 @@
     <row r="8" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>ABRIL</t>
-        </is>
-      </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="B8" s="157" t="n">
+        <v>1380870</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>181211</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>150454</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>147223</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>142469</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>132601</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.096</v>
+      </c>
       <c r="S8" s="18" t="inlineStr">
         <is>
           <t>HUMBERTO</t>
@@ -10844,13 +11510,31 @@
           <t>MARZO</t>
         </is>
       </c>
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="141" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="144" t="n"/>
-      <c r="G6" s="141" t="n"/>
-      <c r="H6" s="32" t="n"/>
+      <c r="B6" s="157" t="n">
+        <v>1958</v>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>1599</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="F6" s="144" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="G6" s="141" t="n">
+        <v>359</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1834</v>
+      </c>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="141" t="n"/>
       <c r="K6" s="32" t="n"/>
@@ -10872,13 +11556,31 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B7" s="157" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="141" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="141" t="n"/>
-      <c r="H7" s="32" t="n"/>
+      <c r="B7" s="157" t="n">
+        <v>4409</v>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="n">
+        <v>3530</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>V27</t>
+        </is>
+      </c>
+      <c r="G7" s="141" t="n">
+        <v>879</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1994</v>
+      </c>
       <c r="I7" s="33" t="n"/>
       <c r="J7" s="141" t="n"/>
       <c r="K7" s="32" t="n"/>
@@ -10900,22 +11602,64 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="141" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="141" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="33" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="32" t="n"/>
+      <c r="B8" s="157" t="n">
+        <v>8829</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="n">
+        <v>3194</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>V34</t>
+        </is>
+      </c>
+      <c r="G8" s="141" t="n">
+        <v>2787</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="J8" s="141" t="n">
+        <v>1314</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="M8" s="141" t="n">
+        <v>949</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="O8" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P8" s="142" t="n">
+        <v>585</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0.0663</v>
+      </c>
       <c r="S8" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -11292,11 +12036,11 @@
     <row r="6" ht="23.25" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>FEBRERO</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="B6" s="141" t="n">
-        <v>1217167</v>
+        <v>1161667</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>1</v>
@@ -11341,7 +12085,9 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="B8" s="141" t="n"/>
+      <c r="B8" s="141" t="n">
+        <v>1144517</v>
+      </c>
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="141" t="n"/>
       <c r="E8" s="17" t="n"/>
@@ -11356,7 +12102,9 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="B9" s="141" t="n"/>
+      <c r="B9" s="141" t="n">
+        <v>1126754</v>
+      </c>
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="141" t="n"/>
       <c r="E9" s="17" t="n"/>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -6956,21 +6956,47 @@
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B9" s="125" t="n"/>
-      <c r="C9" s="61" t="n"/>
-      <c r="D9" s="125" t="n"/>
-      <c r="E9" s="61" t="n"/>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="61" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="61" t="n"/>
-      <c r="J9" s="125" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="125" t="n"/>
-      <c r="M9" s="61" t="n"/>
+      <c r="B9" s="125" t="n">
+        <v>1553183</v>
+      </c>
+      <c r="C9" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="125" t="n">
+        <v>169955</v>
+      </c>
+      <c r="E9" s="61" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="F9" s="125" t="n">
+        <v>1030490</v>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="H9" s="125" t="n">
+        <v>79437</v>
+      </c>
+      <c r="I9" s="61" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="J9" s="125" t="n">
+        <v>19073</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="L9" s="125" t="n">
+        <v>194393</v>
+      </c>
+      <c r="M9" s="61" t="n">
+        <v>0.1641</v>
+      </c>
       <c r="N9" s="125" t="n"/>
       <c r="O9" s="61" t="n"/>
-      <c r="P9" s="126" t="n"/>
+      <c r="P9" s="126" t="n">
+        <v>1184720</v>
+      </c>
     </row>
     <row r="10" ht="23.25" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
@@ -6978,21 +7004,47 @@
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B10" s="125" t="n"/>
-      <c r="C10" s="61" t="n"/>
-      <c r="D10" s="125" t="n"/>
-      <c r="E10" s="61" t="n"/>
-      <c r="F10" s="125" t="n"/>
-      <c r="G10" s="61" t="n"/>
-      <c r="H10" s="125" t="n"/>
-      <c r="I10" s="61" t="n"/>
-      <c r="J10" s="125" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="125" t="n"/>
-      <c r="M10" s="61" t="n"/>
+      <c r="B10" s="125" t="n">
+        <v>1155493</v>
+      </c>
+      <c r="C10" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="125" t="n">
+        <v>122087</v>
+      </c>
+      <c r="E10" s="61" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="F10" s="125" t="n">
+        <v>1157835</v>
+      </c>
+      <c r="G10" s="61" t="n">
+        <v>0.8494</v>
+      </c>
+      <c r="H10" s="125" t="n">
+        <v>141683</v>
+      </c>
+      <c r="I10" s="61" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="J10" s="125" t="n">
+        <v>16280</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="L10" s="125" t="n">
+        <v>188087</v>
+      </c>
+      <c r="M10" s="61" t="n">
+        <v>0.138</v>
+      </c>
       <c r="N10" s="125" t="n"/>
       <c r="O10" s="61" t="n"/>
-      <c r="P10" s="126" t="n"/>
+      <c r="P10" s="126" t="n">
+        <v>1363176</v>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -7518,25 +7570,67 @@
     <row r="9" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B9" s="140" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="66" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="66" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="66" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="66" t="n"/>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B9" s="140" t="n">
+        <v>1553183</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>338235</v>
+      </c>
+      <c r="E9" s="64" t="n">
+        <v>0.2178</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>247834</v>
+      </c>
+      <c r="H9" s="66" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>200807</v>
+      </c>
+      <c r="K9" s="66" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>167328</v>
+      </c>
+      <c r="N9" s="66" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>123675</v>
+      </c>
+      <c r="Q9" s="66" t="n">
+        <v>0.0796</v>
+      </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -7546,25 +7640,67 @@
     <row r="10" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>JUNIO</t>
-        </is>
-      </c>
-      <c r="B10" s="140" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="66" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="66" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="66" t="n"/>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B10" s="140" t="n">
+        <v>1155493</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>289963</v>
+      </c>
+      <c r="E10" s="64" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>250031</v>
+      </c>
+      <c r="H10" s="66" t="n">
+        <v>0.2164</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>238025</v>
+      </c>
+      <c r="K10" s="66" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>200058</v>
+      </c>
+      <c r="N10" s="66" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>122984</v>
+      </c>
+      <c r="Q10" s="66" t="n">
+        <v>0.1064</v>
+      </c>
       <c r="S10" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -8262,22 +8398,64 @@
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+      <c r="B9" s="157" t="n">
+        <v>169955</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>31121</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>27065</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>18295</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>17225</v>
+      </c>
+      <c r="N9" s="32" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>16274</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.0958</v>
+      </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -8290,22 +8468,64 @@
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+      <c r="B10" s="157" t="n">
+        <v>122087</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>22324</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>16426</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>15978</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>15702</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>15605</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.1278</v>
+      </c>
       <c r="S10" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -8982,22 +9202,64 @@
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="141" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+      <c r="B9" s="157" t="n">
+        <v>194393</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>35528</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>34434</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>25321</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>24039</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P9" s="141" t="n">
+        <v>22037</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.1134</v>
+      </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -9010,22 +9272,64 @@
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="141" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+      <c r="B10" s="157" t="n">
+        <v>188087</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>30255</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>27977</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>27324</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>25840</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P10" s="141" t="n">
+        <v>21283</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.1132</v>
+      </c>
       <c r="S10" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -9629,25 +9933,67 @@
     <row r="9" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B9" s="157" t="n">
+        <v>1030490</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>154335</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>135027</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>123177</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>122952</v>
+      </c>
+      <c r="N9" s="32" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>93241</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.0905</v>
+      </c>
       <c r="S9" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -9657,25 +10003,67 @@
     <row r="10" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>JUNIO</t>
-        </is>
-      </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B10" s="157" t="n">
+        <v>1157835</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>168694</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>127884</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>127265</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>118146</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>117743</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.1017</v>
+      </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -10307,25 +10695,67 @@
     <row r="9" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B9" s="157" t="n">
+        <v>79437</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>14729</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>13909</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>11945</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>10794</v>
+      </c>
+      <c r="N9" s="32" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>10046</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.1265</v>
+      </c>
       <c r="S9" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -10335,25 +10765,67 @@
     <row r="10" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>JUNIO</t>
-        </is>
-      </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B10" s="157" t="n">
+        <v>141683</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>26174</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>21463</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>20379</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>17567</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>12390</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.08740000000000001</v>
+      </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -10985,25 +11457,67 @@
     <row r="9" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>MAYO</t>
-        </is>
-      </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="B9" s="157" t="n">
+        <v>1184720</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>162096</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>150678</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>145762</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>141759</v>
+      </c>
+      <c r="N9" s="32" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>103160</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.0871</v>
+      </c>
       <c r="S9" s="25" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -11013,25 +11527,67 @@
     <row r="10" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>JUNIO</t>
-        </is>
-      </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="B10" s="157" t="n">
+        <v>1363176</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>194541</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>152527</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>146229</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>142238</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>141741</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.104</v>
+      </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -11672,22 +12228,64 @@
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B9" s="157" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="141" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="141" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="32" t="n"/>
+      <c r="B9" s="157" t="n">
+        <v>19073</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D9" s="141" t="n">
+        <v>6403</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="G9" s="141" t="n">
+        <v>3198</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1677</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
+      <c r="J9" s="141" t="n">
+        <v>3100</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M9" s="141" t="n">
+        <v>2712</v>
+      </c>
+      <c r="N9" s="32" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="n">
+        <v>1903</v>
+      </c>
+      <c r="Q9" s="32" t="n">
+        <v>0.0998</v>
+      </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>OFICINA</t>
@@ -11700,22 +12298,64 @@
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="141" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="141" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="141" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="141" t="n"/>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="33" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="32" t="n"/>
+      <c r="B10" s="157" t="n">
+        <v>16280</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="n">
+        <v>6870</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>V23</t>
+        </is>
+      </c>
+      <c r="G10" s="141" t="n">
+        <v>4229</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>3847</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="M10" s="141" t="n">
+        <v>749</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="n">
+        <v>585</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>0.0359</v>
+      </c>
       <c r="S10" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -12119,7 +12759,9 @@
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="B10" s="141" t="n"/>
+      <c r="B10" s="141" t="n">
+        <v>1103443</v>
+      </c>
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="141" t="n"/>
       <c r="E10" s="17" t="n"/>
@@ -12134,7 +12776,9 @@
           <t>JULIO</t>
         </is>
       </c>
-      <c r="B11" s="141" t="n"/>
+      <c r="B11" s="141" t="n">
+        <v>1063756</v>
+      </c>
       <c r="C11" s="17" t="n"/>
       <c r="D11" s="141" t="n"/>
       <c r="E11" s="17" t="n"/>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -7052,21 +7052,47 @@
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B11" s="125" t="n"/>
-      <c r="C11" s="61" t="n"/>
-      <c r="D11" s="125" t="n"/>
-      <c r="E11" s="61" t="n"/>
-      <c r="F11" s="125" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="125" t="n"/>
-      <c r="I11" s="61" t="n"/>
-      <c r="J11" s="125" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="125" t="n"/>
-      <c r="M11" s="61" t="n"/>
+      <c r="B11" s="125" t="n">
+        <v>1476747</v>
+      </c>
+      <c r="C11" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="125" t="n">
+        <v>140286</v>
+      </c>
+      <c r="E11" s="61" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="F11" s="125" t="n">
+        <v>1073301</v>
+      </c>
+      <c r="G11" s="61" t="n">
+        <v>0.8522999999999999</v>
+      </c>
+      <c r="H11" s="125" t="n">
+        <v>103509</v>
+      </c>
+      <c r="I11" s="61" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="J11" s="125" t="n">
+        <v>4788</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="L11" s="125" t="n">
+        <v>196893</v>
+      </c>
+      <c r="M11" s="61" t="n">
+        <v>0.1564</v>
+      </c>
       <c r="N11" s="125" t="n"/>
       <c r="O11" s="61" t="n"/>
-      <c r="P11" s="126" t="n"/>
+      <c r="P11" s="126" t="n">
+        <v>1259266</v>
+      </c>
     </row>
     <row r="12" ht="23.25" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
@@ -7710,25 +7736,67 @@
     <row r="11" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B11" s="140" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="66" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="66" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="66" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="66" t="n"/>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B11" s="140" t="n">
+        <v>1476747</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>335674</v>
+      </c>
+      <c r="E11" s="64" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>248812</v>
+      </c>
+      <c r="H11" s="66" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>170653</v>
+      </c>
+      <c r="K11" s="66" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>166051</v>
+      </c>
+      <c r="N11" s="66" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="n">
+        <v>116263</v>
+      </c>
+      <c r="Q11" s="66" t="n">
+        <v>0.07870000000000001</v>
+      </c>
       <c r="S11" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -8538,22 +8606,64 @@
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+      <c r="B11" s="157" t="n">
+        <v>140286</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>24028</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>20411</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>16320</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>15679</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="n">
+        <v>14652</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0.1044</v>
+      </c>
       <c r="S11" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -9342,22 +9452,64 @@
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="19" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="141" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+      <c r="B11" s="157" t="n">
+        <v>196893</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>34777</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>32166</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>27190</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>23333</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P11" s="141" t="n">
+        <v>19226</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0.09760000000000001</v>
+      </c>
       <c r="S11" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -10073,25 +10225,67 @@
     <row r="11" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B11" s="157" t="n">
+        <v>1073301</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>138562</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>117989</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>116022</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>114361</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="n">
+        <v>91896</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0.0856</v>
+      </c>
       <c r="S11" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -10835,25 +11029,67 @@
     <row r="11" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B11" s="157" t="n">
+        <v>103509</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>20820</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>20160</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>14400</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>13713</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="n">
+        <v>8890</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0.0859</v>
+      </c>
       <c r="S11" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -11597,25 +11833,67 @@
     <row r="11" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>JULIO</t>
-        </is>
-      </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+          <t>AGOSTO</t>
+        </is>
+      </c>
+      <c r="B11" s="157" t="n">
+        <v>1259266</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>155424</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>138985</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>126358</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="M11" s="141" t="n">
+        <v>126162</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="n">
+        <v>105846</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0.08409999999999999</v>
+      </c>
       <c r="S11" s="144" t="inlineStr">
         <is>
           <t>TRANSFER. / DEPTOS.</t>
@@ -12368,22 +12646,56 @@
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B11" s="157" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="141" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="141" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="141" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="141" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="142" t="n"/>
-      <c r="Q11" s="32" t="n"/>
+      <c r="B11" s="157" t="n">
+        <v>4788</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="n">
+        <v>2648</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G11" s="141" t="n">
+        <v>1378</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>762</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr"/>
+      <c r="M11" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr"/>
+      <c r="P11" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -12793,7 +13105,9 @@
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="B12" s="141" t="n"/>
+      <c r="B12" s="141" t="n">
+        <v>1053199</v>
+      </c>
       <c r="C12" s="17" t="n"/>
       <c r="D12" s="141" t="n"/>
       <c r="E12" s="17" t="n"/>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -7100,21 +7100,47 @@
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B12" s="125" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="125" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="125" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="125" t="n"/>
-      <c r="I12" s="61" t="n"/>
-      <c r="J12" s="125" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="125" t="n"/>
-      <c r="M12" s="61" t="n"/>
+      <c r="B12" s="125" t="n">
+        <v>1457328</v>
+      </c>
+      <c r="C12" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="125" t="n">
+        <v>163265</v>
+      </c>
+      <c r="E12" s="61" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="F12" s="125" t="n">
+        <v>1041594</v>
+      </c>
+      <c r="G12" s="61" t="n">
+        <v>0.8806</v>
+      </c>
+      <c r="H12" s="125" t="n">
+        <v>97679</v>
+      </c>
+      <c r="I12" s="61" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="J12" s="125" t="n">
+        <v>829</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="L12" s="125" t="n">
+        <v>161871</v>
+      </c>
+      <c r="M12" s="61" t="n">
+        <v>0.1368</v>
+      </c>
       <c r="N12" s="125" t="n"/>
       <c r="O12" s="61" t="n"/>
-      <c r="P12" s="126" t="n"/>
+      <c r="P12" s="126" t="n">
+        <v>1182875</v>
+      </c>
     </row>
     <row r="13" ht="23.25" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -7122,21 +7148,47 @@
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B13" s="125" t="n"/>
-      <c r="C13" s="61" t="n"/>
-      <c r="D13" s="125" t="n"/>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="125" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="125" t="n"/>
-      <c r="I13" s="61" t="n"/>
-      <c r="J13" s="125" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="125" t="n"/>
-      <c r="M13" s="61" t="n"/>
+      <c r="B13" s="125" t="n">
+        <v>1387167</v>
+      </c>
+      <c r="C13" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="125" t="n">
+        <v>148882</v>
+      </c>
+      <c r="E13" s="61" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="F13" s="125" t="n">
+        <v>1056064</v>
+      </c>
+      <c r="G13" s="61" t="n">
+        <v>0.8877</v>
+      </c>
+      <c r="H13" s="125" t="n">
+        <v>99650</v>
+      </c>
+      <c r="I13" s="61" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="J13" s="125" t="n">
+        <v>13024</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="L13" s="125" t="n">
+        <v>123852</v>
+      </c>
+      <c r="M13" s="61" t="n">
+        <v>0.1041</v>
+      </c>
       <c r="N13" s="125" t="n"/>
       <c r="O13" s="61" t="n"/>
-      <c r="P13" s="126" t="n"/>
+      <c r="P13" s="126" t="n">
+        <v>1189602</v>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
@@ -7806,25 +7858,67 @@
     <row r="12" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B12" s="140" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="66" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="66" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="66" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="66" t="n"/>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B12" s="140" t="n">
+        <v>1457328</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>336188</v>
+      </c>
+      <c r="E12" s="64" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>287007</v>
+      </c>
+      <c r="H12" s="66" t="n">
+        <v>0.1969</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>173114</v>
+      </c>
+      <c r="K12" s="66" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>139923</v>
+      </c>
+      <c r="N12" s="66" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="n">
+        <v>118136</v>
+      </c>
+      <c r="Q12" s="66" t="n">
+        <v>0.08110000000000001</v>
+      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -7834,25 +7928,67 @@
     <row r="13" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B13" s="140" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="66" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="66" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="66" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="66" t="n"/>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B13" s="140" t="n">
+        <v>1387167</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>280947</v>
+      </c>
+      <c r="E13" s="64" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>243835</v>
+      </c>
+      <c r="H13" s="66" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>203100</v>
+      </c>
+      <c r="K13" s="66" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>149587</v>
+      </c>
+      <c r="N13" s="66" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>111902</v>
+      </c>
+      <c r="Q13" s="66" t="n">
+        <v>0.08069999999999999</v>
+      </c>
       <c r="S13" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -8676,22 +8812,64 @@
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+      <c r="B12" s="157" t="n">
+        <v>163265</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>25115</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>22030</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>21381</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>19956</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="n">
+        <v>17786</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0.1089</v>
+      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -8704,22 +8882,64 @@
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+      <c r="B13" s="157" t="n">
+        <v>148882</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>25575</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>22628</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>20863</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>18703</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>17061</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.1146</v>
+      </c>
       <c r="S13" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -9522,22 +9742,64 @@
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="141" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+      <c r="B12" s="157" t="n">
+        <v>161871</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>35149</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>27333</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>21196</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>19713</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="P12" s="141" t="n">
+        <v>9963</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0.0615</v>
+      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -9550,22 +9812,64 @@
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="141" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+      <c r="B13" s="157" t="n">
+        <v>123852</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>25906</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>15983</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>14491</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>13936</v>
+      </c>
+      <c r="N13" s="19" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P13" s="141" t="n">
+        <v>12834</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.1036</v>
+      </c>
       <c r="S13" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -10295,25 +10599,67 @@
     <row r="12" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B12" s="157" t="n">
+        <v>1041594</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>151823</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>141031</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>118262</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>91796</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="n">
+        <v>88788</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0.0852</v>
+      </c>
       <c r="S12" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -10323,25 +10669,67 @@
     <row r="13" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B13" s="157" t="n">
+        <v>1056064</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>197251</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>139601</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>123517</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>93781</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>87270</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.08260000000000001</v>
+      </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -11099,25 +11487,67 @@
     <row r="12" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B12" s="157" t="n">
+        <v>97679</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>18256</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>16536</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>14775</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>13831</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="n">
+        <v>10428</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0.1068</v>
+      </c>
       <c r="S12" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -11127,25 +11557,67 @@
     <row r="13" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B13" s="157" t="n">
+        <v>99650</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>26043</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>17172</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>15841</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>9058</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>7266</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.07290000000000001</v>
+      </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -11903,25 +12375,67 @@
     <row r="12" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>AGOSTO</t>
-        </is>
-      </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+          <t>SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="B12" s="157" t="n">
+        <v>1182875</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>164719</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>159752</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>135242</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="M12" s="141" t="n">
+        <v>108699</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="n">
+        <v>108681</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0.0919</v>
+      </c>
       <c r="S12" s="145" t="inlineStr">
         <is>
           <t>V1 COCO</t>
@@ -11931,25 +12445,67 @@
     <row r="13" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+          <t>OCTUBRE</t>
+        </is>
+      </c>
+      <c r="B13" s="157" t="n">
+        <v>1189602</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>206295</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>167288</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>128228</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>106835</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>104855</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.0881</v>
+      </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -12708,22 +13264,52 @@
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B12" s="157" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="141" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="141" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="141" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="141" t="n"/>
-      <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="142" t="n"/>
-      <c r="Q12" s="32" t="n"/>
+      <c r="B12" s="157" t="n">
+        <v>829</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="n">
+        <v>719</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="G12" s="141" t="n">
+        <v>110</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr"/>
+      <c r="J12" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="33" t="inlineStr"/>
+      <c r="M12" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr"/>
+      <c r="P12" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>V2 CARLOS</t>
@@ -12736,22 +13322,64 @@
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="141" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="141" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="141" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="141" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="33" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="32" t="n"/>
+      <c r="B13" s="157" t="n">
+        <v>13024</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D13" s="141" t="n">
+        <v>3229</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G13" s="141" t="n">
+        <v>3111</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J13" s="141" t="n">
+        <v>3026</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="M13" s="141" t="n">
+        <v>2969</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="n">
+        <v>689</v>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>0.0529</v>
+      </c>
       <c r="S13" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -13122,7 +13750,9 @@
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="B13" s="141" t="n"/>
+      <c r="B13" s="141" t="n">
+        <v>1005817</v>
+      </c>
       <c r="C13" s="17" t="n"/>
       <c r="D13" s="141" t="n"/>
       <c r="E13" s="17" t="n"/>
@@ -13137,7 +13767,9 @@
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="B14" s="141" t="n"/>
+      <c r="B14" s="141" t="n">
+        <v>1014752</v>
+      </c>
       <c r="C14" s="17" t="n"/>
       <c r="D14" s="141" t="n"/>
       <c r="E14" s="17" t="n"/>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_PARA_JUNTA_MENSUAL_2025.xlsx
@@ -7196,21 +7196,47 @@
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="B14" s="125" t="n"/>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="125" t="n"/>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="125" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="61" t="n"/>
-      <c r="J14" s="125" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="125" t="n"/>
-      <c r="M14" s="61" t="n"/>
+      <c r="B14" s="125" t="n">
+        <v>1652266</v>
+      </c>
+      <c r="C14" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="125" t="n">
+        <v>155904</v>
+      </c>
+      <c r="E14" s="61" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="F14" s="125" t="n">
+        <v>1306688</v>
+      </c>
+      <c r="G14" s="61" t="n">
+        <v>0.8859</v>
+      </c>
+      <c r="H14" s="125" t="n">
+        <v>71268</v>
+      </c>
+      <c r="I14" s="61" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="J14" s="125" t="n">
+        <v>1212</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="L14" s="125" t="n">
+        <v>142886</v>
+      </c>
+      <c r="M14" s="61" t="n">
+        <v>0.0969</v>
+      </c>
       <c r="N14" s="125" t="n"/>
       <c r="O14" s="61" t="n"/>
-      <c r="P14" s="126" t="n"/>
+      <c r="P14" s="126" t="n">
+        <v>1474935</v>
+      </c>
     </row>
     <row r="15" ht="23.25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -7218,21 +7244,47 @@
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="B15" s="127" t="n"/>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="127" t="n"/>
-      <c r="E15" s="62" t="n"/>
-      <c r="F15" s="127" t="n"/>
-      <c r="G15" s="62" t="n"/>
-      <c r="H15" s="127" t="n"/>
-      <c r="I15" s="62" t="n"/>
-      <c r="J15" s="127" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="127" t="n"/>
-      <c r="M15" s="62" t="n"/>
+      <c r="B15" s="127" t="n">
+        <v>1485306</v>
+      </c>
+      <c r="C15" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="127" t="n">
+        <v>138976</v>
+      </c>
+      <c r="E15" s="62" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="F15" s="127" t="n">
+        <v>1040437</v>
+      </c>
+      <c r="G15" s="62" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="H15" s="127" t="n">
+        <v>93902</v>
+      </c>
+      <c r="I15" s="62" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="J15" s="127" t="n">
+        <v>7523</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="L15" s="127" t="n">
+        <v>184948</v>
+      </c>
+      <c r="M15" s="62" t="n">
+        <v>0.1522</v>
+      </c>
       <c r="N15" s="127" t="n"/>
       <c r="O15" s="62" t="n"/>
-      <c r="P15" s="128" t="n"/>
+      <c r="P15" s="128" t="n">
+        <v>1215442</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7998,25 +8050,67 @@
     <row r="14" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B14" s="140" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="66" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="66" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="142" t="n"/>
-      <c r="Q14" s="66" t="n"/>
+          <t>NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="B14" s="140" t="n">
+        <v>1652266</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>331147</v>
+      </c>
+      <c r="E14" s="64" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>326687</v>
+      </c>
+      <c r="H14" s="66" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>184698</v>
+      </c>
+      <c r="K14" s="66" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>154297</v>
+      </c>
+      <c r="N14" s="66" t="n">
+        <v>0.0934</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P14" s="142" t="n">
+        <v>148292</v>
+      </c>
+      <c r="Q14" s="66" t="n">
+        <v>0.0898</v>
+      </c>
       <c r="S14" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -8026,25 +8120,67 @@
     <row r="15" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A15" s="40" t="inlineStr">
         <is>
-          <t>NOVIEMBRE</t>
-        </is>
-      </c>
-      <c r="B15" s="140" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="141" t="n"/>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="141" t="n"/>
-      <c r="H15" s="66" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="141" t="n"/>
-      <c r="K15" s="66" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="141" t="n"/>
-      <c r="N15" s="66" t="n"/>
-      <c r="O15" s="33" t="n"/>
-      <c r="P15" s="142" t="n"/>
-      <c r="Q15" s="66" t="n"/>
+          <t>DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="B15" s="140" t="n">
+        <v>1485306</v>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="141" t="n">
+        <v>318772</v>
+      </c>
+      <c r="E15" s="64" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="141" t="n">
+        <v>255372</v>
+      </c>
+      <c r="H15" s="66" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J15" s="141" t="n">
+        <v>193618</v>
+      </c>
+      <c r="K15" s="66" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M15" s="141" t="n">
+        <v>163570</v>
+      </c>
+      <c r="N15" s="66" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="O15" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P15" s="142" t="n">
+        <v>117679</v>
+      </c>
+      <c r="Q15" s="66" t="n">
+        <v>0.07920000000000001</v>
+      </c>
       <c r="S15" s="148" t="inlineStr">
         <is>
           <t>V37 EDGARDO</t>
@@ -8952,22 +9088,64 @@
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="142" t="n"/>
-      <c r="Q14" s="32" t="n"/>
+      <c r="B14" s="157" t="n">
+        <v>155904</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>22218</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>20244</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>19226</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>17138</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" s="142" t="n">
+        <v>16723</v>
+      </c>
+      <c r="Q14" s="32" t="n">
+        <v>0.1073</v>
+      </c>
       <c r="S14" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -8980,22 +9158,64 @@
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="B15" s="159" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="150" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="150" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="150" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="150" t="n"/>
-      <c r="N15" s="35" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="151" t="n"/>
-      <c r="Q15" s="35" t="n"/>
+      <c r="B15" s="159" t="n">
+        <v>138976</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="150" t="n">
+        <v>34230</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="150" t="n">
+        <v>19675</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J15" s="150" t="n">
+        <v>17044</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M15" s="150" t="n">
+        <v>15128</v>
+      </c>
+      <c r="N15" s="35" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="O15" s="34" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P15" s="151" t="n">
+        <v>10751</v>
+      </c>
+      <c r="Q15" s="35" t="n">
+        <v>0.0774</v>
+      </c>
       <c r="S15" s="148" t="inlineStr">
         <is>
           <t>V37 EDGARDO</t>
@@ -9882,22 +10102,64 @@
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="19" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="141" t="n"/>
-      <c r="Q14" s="32" t="n"/>
+      <c r="B14" s="157" t="n">
+        <v>142886</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>27058</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>21620</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>17548</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>15508</v>
+      </c>
+      <c r="N14" s="19" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P14" s="141" t="n">
+        <v>11941</v>
+      </c>
+      <c r="Q14" s="32" t="n">
+        <v>0.08359999999999999</v>
+      </c>
       <c r="S14" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -9910,22 +10172,64 @@
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="B15" s="159" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="150" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="150" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="150" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="150" t="n"/>
-      <c r="N15" s="37" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="150" t="n"/>
-      <c r="Q15" s="35" t="n"/>
+      <c r="B15" s="159" t="n">
+        <v>184948</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D15" s="150" t="n">
+        <v>35709</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="G15" s="150" t="n">
+        <v>29037</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="J15" s="150" t="n">
+        <v>24121</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="M15" s="150" t="n">
+        <v>20493</v>
+      </c>
+      <c r="N15" s="37" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="O15" s="34" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="P15" s="150" t="n">
+        <v>16748</v>
+      </c>
+      <c r="Q15" s="35" t="n">
+        <v>0.0906</v>
+      </c>
       <c r="S15" s="148" t="inlineStr">
         <is>
           <t>V37 EDGARDO</t>
@@ -10739,25 +11043,67 @@
     <row r="14" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="142" t="n"/>
-      <c r="Q14" s="32" t="n"/>
+          <t>NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="B14" s="157" t="n">
+        <v>1306688</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>201030</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>148682</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>131500</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>109480</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="P14" s="142" t="n">
+        <v>102325</v>
+      </c>
+      <c r="Q14" s="32" t="n">
+        <v>0.07829999999999999</v>
+      </c>
       <c r="S14" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -10767,25 +11113,67 @@
     <row r="15" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A15" s="40" t="inlineStr">
         <is>
-          <t>NOVIEMBRE</t>
-        </is>
-      </c>
-      <c r="B15" s="157" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="141" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="141" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="141" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="141" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="33" t="n"/>
-      <c r="P15" s="142" t="n"/>
-      <c r="Q15" s="32" t="n"/>
+          <t>DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="B15" s="157" t="n">
+        <v>1040437</v>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D15" s="141" t="n">
+        <v>197276</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G15" s="141" t="n">
+        <v>132852</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J15" s="141" t="n">
+        <v>124088</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M15" s="141" t="n">
+        <v>116172</v>
+      </c>
+      <c r="N15" s="32" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="O15" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="P15" s="142" t="n">
+        <v>74617</v>
+      </c>
+      <c r="Q15" s="32" t="n">
+        <v>0.0717</v>
+      </c>
       <c r="S15" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -11627,25 +12015,67 @@
     <row r="14" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="142" t="n"/>
-      <c r="Q14" s="32" t="n"/>
+          <t>NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="B14" s="157" t="n">
+        <v>71268</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>17717</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>13041</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>10570</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>6402</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="P14" s="142" t="n">
+        <v>5801</v>
+      </c>
+      <c r="Q14" s="32" t="n">
+        <v>0.0814</v>
+      </c>
       <c r="S14" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -11655,25 +12085,67 @@
     <row r="15" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A15" s="40" t="inlineStr">
         <is>
-          <t>NOVIEMBRE</t>
-        </is>
-      </c>
-      <c r="B15" s="157" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="141" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="141" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="141" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="141" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="33" t="n"/>
-      <c r="P15" s="142" t="n"/>
-      <c r="Q15" s="32" t="n"/>
+          <t>DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="B15" s="157" t="n">
+        <v>93902</v>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D15" s="141" t="n">
+        <v>23270</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G15" s="141" t="n">
+        <v>13459</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="J15" s="141" t="n">
+        <v>12241</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M15" s="141" t="n">
+        <v>11776</v>
+      </c>
+      <c r="N15" s="32" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="O15" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="P15" s="142" t="n">
+        <v>10299</v>
+      </c>
+      <c r="Q15" s="32" t="n">
+        <v>0.1097</v>
+      </c>
       <c r="S15" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -12515,25 +12987,67 @@
     <row r="14" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>OCTUBRE</t>
-        </is>
-      </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="141" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="141" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="141" t="n"/>
-      <c r="N14" s="32" t="n"/>
-      <c r="O14" s="33" t="n"/>
-      <c r="P14" s="142" t="n"/>
-      <c r="Q14" s="32" t="n"/>
+          <t>NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="B14" s="157" t="n">
+        <v>1474935</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>209069</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="G14" s="141" t="n">
+        <v>153896</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>136892</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="M14" s="141" t="n">
+        <v>135069</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="P14" s="142" t="n">
+        <v>117009</v>
+      </c>
+      <c r="Q14" s="32" t="n">
+        <v>0.0793</v>
+      </c>
       <c r="S14" s="146" t="inlineStr">
         <is>
           <t>V22 SALVADOR</t>
@@ -12543,25 +13057,67 @@
     <row r="15" ht="23.25" customFormat="1" customHeight="1" s="4">
       <c r="A15" s="40" t="inlineStr">
         <is>
-          <t>NOVIEMBRE</t>
-        </is>
-      </c>
-      <c r="B15" s="157" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="141" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="141" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="141" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="141" t="n"/>
-      <c r="N15" s="32" t="n"/>
-      <c r="O15" s="33" t="n"/>
-      <c r="P15" s="142" t="n"/>
-      <c r="Q15" s="32" t="n"/>
+          <t>DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="B15" s="157" t="n">
+        <v>1215442</v>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D15" s="141" t="n">
+        <v>215551</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0.1773</v>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G15" s="141" t="n">
+        <v>155921</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="J15" s="141" t="n">
+        <v>153048</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="M15" s="141" t="n">
+        <v>128883</v>
+      </c>
+      <c r="N15" s="32" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="O15" s="33" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="P15" s="142" t="n">
+        <v>97336</v>
+      </c>
+      <c r="Q15" s="32" t="n">
+        <v>0.0801</v>
+      </c>
       <c r="S15" s="147" t="inlineStr">
         <is>
           <t>V27 SANTIAGO</t>
@@ -13392,10 +13948,20 @@
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="B14" s="157" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="141" t="n"/>
-      <c r="E14" s="32" t="n"/>
+      <c r="B14" s="157" t="n">
+        <v>1212</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="n">
+        <v>1212</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>1</v>
+      </c>
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="141" t="n"/>
       <c r="H14" s="32" t="n"/>
@@ -13420,16 +13986,42 @@
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="B15" s="159" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="150" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="150" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="150" t="n"/>
-      <c r="K15" s="35" t="n"/>
+      <c r="B15" s="159" t="n">
+        <v>7523</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="D15" s="150" t="n">
+        <v>3849</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G15" s="150" t="n">
+        <v>2715</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="J15" s="150" t="n">
+        <v>689</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>0.0916</v>
+      </c>
       <c r="L15" s="34" t="n"/>
       <c r="M15" s="150" t="n"/>
       <c r="N15" s="35" t="n"/>
@@ -13784,7 +14376,9 @@
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="B15" s="141" t="n"/>
+      <c r="B15" s="141" t="n">
+        <v>1065332</v>
+      </c>
       <c r="C15" s="17" t="n"/>
       <c r="D15" s="141" t="n"/>
       <c r="E15" s="17" t="n"/>
@@ -13799,7 +14393,9 @@
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="B16" s="141" t="n"/>
+      <c r="B16" s="141" t="n">
+        <v>1150227</v>
+      </c>
       <c r="C16" s="17" t="n"/>
       <c r="D16" s="141" t="n"/>
       <c r="E16" s="17" t="n"/>
